--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1,251 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AbyssalBlessingInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="AbyssalBlessingInfo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>icon_res</t>
-  </si>
-  <si>
-    <t>buff_ids</t>
-  </si>
-  <si>
-    <t>name[language]</t>
-  </si>
-  <si>
-    <t>details[language]</t>
-  </si>
-  <si>
-    <t>remark</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>图标名字</t>
-  </si>
-  <si>
-    <t>名字-中文</t>
-  </si>
-  <si>
-    <t>描述中文</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>增殖-随机复制一个已有的魔物</t>
-  </si>
-  <si>
-    <t>钱多多-每一次击杀有10%的概率多掉落一次魔晶</t>
-  </si>
-  <si>
-    <t>强征健体-所有魔物体力增加10%</t>
-  </si>
-  <si>
-    <t>时光沙漏-所有魔物放置CD减少10%</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -545,156 +471,160 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -750,11 +680,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1043,173 +1036,706 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F80"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.5"/>
-    <col min="2" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="30.5" customWidth="1"/>
-    <col min="6" max="6" width="42.875" customWidth="1"/>
-    <col min="7" max="7" width="25.125" customWidth="1"/>
+    <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
+    <col width="17.5" customWidth="1" style="1" min="2" max="5"/>
+    <col width="17.125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" style="1" min="7" max="7"/>
+    <col width="42.875" customWidth="1" style="1" min="8" max="8"/>
+    <col width="25.125" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>icon_res</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>parent_id</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>buff_ids</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>name[language]</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>details[language_1]</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>图标名字</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>父级深渊馈赠ID</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>buff_ids</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>名字-中文</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>描述中文</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
+        <v>1000001001</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E4" s="0" t="n">
+        <v>3000100001</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>1000001001</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>1000001001</v>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>增殖-随机复制一个已有的魔物</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
+        <v>2000001001</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E5" s="0" t="n">
+        <v>3000200001</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>2000001001</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>2000001001</v>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>钱多多-每一次击杀有10%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n">
+        <v>2000001002</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>2000001001</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E6" s="0" t="n">
+        <v>3000200002</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>2000001002</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>2000001002</v>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>钱多多-每一次击杀有20%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="n">
+        <v>2000001003</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>2000001002</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E7" s="0" t="n">
+        <v>3000200003</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>2000001003</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>2000001003</v>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>钱多多-每一次击杀有30%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="n">
+        <v>2000001004</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>2000001003</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E8" s="0" t="n">
+        <v>3000200004</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>2000001004</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>2000001004</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>钱多多-每一次击杀有40%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n">
+        <v>2000001005</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>2000001004</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E9" s="0" t="n">
+        <v>3000200005</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>2000001005</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>2000001005</v>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>钱多多-每一次击杀有50%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
+        <v>2000002001</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>2000002001</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>2000002001</v>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>强身健体-所有魔物体力增加10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
+        <v>2000002002</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>2000002001</v>
+      </c>
+      <c r="D11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>1000001001</v>
-      </c>
-      <c r="C4">
-        <v>3000100001</v>
-      </c>
-      <c r="D4">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3000300002</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>2000002002</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>2000002002</v>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>强身健体-所有魔物体力增加20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
+        <v>2000002003</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>2000002002</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3000300003</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>2000002003</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>2000002003</v>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>强身健体-所有魔物体力增加30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="n">
+        <v>2000002004</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>2000002003</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3000300004</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>2000002004</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>2000002004</v>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>强身健体-所有魔物体力增加40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n">
+        <v>2000002005</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>2000002004</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3000300005</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>2000002005</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>2000002005</v>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>强身健体-所有魔物体力增加50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" s="1">
+      <c r="A15" s="0" t="n">
+        <v>2000003001</v>
+      </c>
+      <c r="D15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="E15" s="2" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>2000003001</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>2000003001</v>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>时光沙漏-所有魔物放置CD减少10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n">
+        <v>2000003002</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>2000003001</v>
+      </c>
+      <c r="D16" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>2000001001</v>
-      </c>
-      <c r="C5">
-        <v>3000200001</v>
-      </c>
-      <c r="D5">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3000400002</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>2000003002</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>2000003002</v>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>时光沙漏-所有魔物放置CD减少20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n">
+        <v>2000003003</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>2000003002</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3000400003</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>2000003003</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>2000003003</v>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>时光沙漏-所有魔物放置CD减少30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="n">
+        <v>2000003004</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>2000003003</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3000400004</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>2000003004</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>2000003004</v>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>时光沙漏-所有魔物放置CD减少40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="n">
+        <v>2000003005</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>2000003004</v>
+      </c>
+      <c r="D19" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>2000002001</v>
-      </c>
-      <c r="C6">
-        <v>3000300001</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>2000003001</v>
-      </c>
-      <c r="C7">
-        <v>3000400001</v>
-      </c>
-      <c r="D7">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3000400005</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>2000003005</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>2000003005</v>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>时光沙漏-所有魔物放置CD减少50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2000004001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3000500001</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2000004001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2000004001</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>伤害性极强LV1-所有魔物攻击力增加10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2000004002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2000004001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3000500002</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2000004002</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2000004002</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>伤害性极强LV2-所有魔物攻击力增加20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2000004003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2000004002</v>
+      </c>
+      <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="E7">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3000500003</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2000004003</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2000004003</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>伤害性极强LV3-所有魔物攻击力增加30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2000004004</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2000004003</v>
+      </c>
+      <c r="D23" t="n">
         <v>4</v>
       </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1"/>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="72" ht="12" customHeight="1"/>
-    <row r="73" ht="12" customHeight="1"/>
-    <row r="74" ht="12" customHeight="1"/>
-    <row r="75" ht="12" customHeight="1"/>
-    <row r="76" ht="12" customHeight="1"/>
-    <row r="77" ht="12" customHeight="1"/>
-    <row r="78" ht="12" customHeight="1"/>
-    <row r="79" ht="12" customHeight="1"/>
-    <row r="80" ht="12" customHeight="1"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3000500004</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2000004004</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2000004004</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>伤害性极强LV4-所有魔物攻击力增加40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2000004005</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2000004004</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3000500005</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2000004005</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2000004005</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>伤害性极强LV5-所有魔物攻击力增加50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="1"/>
+    <row r="35" ht="15" customHeight="1" s="1"/>
+    <row r="36" ht="15" customHeight="1" s="1"/>
+    <row r="37" ht="15" customHeight="1" s="1"/>
+    <row r="38" ht="15" customHeight="1" s="1"/>
+    <row r="39" ht="15" customHeight="1" s="1"/>
+    <row r="40" ht="15" customHeight="1" s="1"/>
+    <row r="41" ht="15" customHeight="1" s="1"/>
+    <row r="42" ht="15" customHeight="1" s="1"/>
+    <row r="43" ht="15" customHeight="1" s="1"/>
+    <row r="44" ht="15" customHeight="1" s="1"/>
+    <row r="76" ht="12" customHeight="1" s="1"/>
+    <row r="77" ht="12" customHeight="1" s="1"/>
+    <row r="78" ht="12" customHeight="1" s="1"/>
+    <row r="79" ht="12" customHeight="1" s="1"/>
+    <row r="80" ht="12" customHeight="1" s="1"/>
+    <row r="81" ht="12" customHeight="1" s="1"/>
+    <row r="82" ht="12" customHeight="1" s="1"/>
+    <row r="83" ht="12" customHeight="1" s="1"/>
+    <row r="84" ht="12" customHeight="1" s="1"/>
   </sheetData>
-  <sortState ref="A4:X88">
-    <sortCondition ref="A4"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1583,134 +1583,269 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="0" t="n">
         <v>2000004001</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>3000500001</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="0" t="n">
         <v>2000004001</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="0" t="n">
         <v>2000004001</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV1-所有魔物攻击力增加10%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="0" t="n">
         <v>2000004002</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="0" t="n">
         <v>2000004001</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>3000500002</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="0" t="n">
         <v>2000004002</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="0" t="n">
         <v>2000004002</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV2-所有魔物攻击力增加20%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="0" t="n">
         <v>2000004003</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="0" t="n">
         <v>2000004002</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>3000500003</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="0" t="n">
         <v>2000004003</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="0" t="n">
         <v>2000004003</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV3-所有魔物攻击力增加30%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="0" t="n">
         <v>2000004004</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="0" t="n">
         <v>2000004003</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>3000500004</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="0" t="n">
         <v>2000004004</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="0" t="n">
         <v>2000004004</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV4-所有魔物攻击力增加40%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="0" t="n">
         <v>2000004005</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="0" t="n">
         <v>2000004004</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>3000500005</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="0" t="n">
         <v>2000004005</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="0" t="n">
         <v>2000004005</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV5-所有魔物攻击力增加50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3000600001</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3000600002</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3000600003</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3000600004</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2000005005</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3000600005</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2000005005</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2000005005</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1182,6 +1182,11 @@
       <c r="A4" s="0" t="n">
         <v>1000001001</v>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>abyssal_proliferation</t>
+        </is>
+      </c>
       <c r="D4" s="0" t="n">
         <v>0</v>
       </c>
@@ -1204,6 +1209,11 @@
       <c r="A5" s="0" t="n">
         <v>2000001001</v>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>abyssal_money</t>
+        </is>
+      </c>
       <c r="D5" s="0" t="n">
         <v>1</v>
       </c>
@@ -1226,6 +1236,11 @@
       <c r="A6" s="0" t="n">
         <v>2000001002</v>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>abyssal_money</t>
+        </is>
+      </c>
       <c r="C6" s="0" t="n">
         <v>2000001001</v>
       </c>
@@ -1251,6 +1266,11 @@
       <c r="A7" s="0" t="n">
         <v>2000001003</v>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>abyssal_money</t>
+        </is>
+      </c>
       <c r="C7" s="0" t="n">
         <v>2000001002</v>
       </c>
@@ -1276,6 +1296,11 @@
       <c r="A8" s="0" t="n">
         <v>2000001004</v>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>abyssal_money</t>
+        </is>
+      </c>
       <c r="C8" s="0" t="n">
         <v>2000001003</v>
       </c>
@@ -1301,6 +1326,11 @@
       <c r="A9" s="0" t="n">
         <v>2000001005</v>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>abyssal_money</t>
+        </is>
+      </c>
       <c r="C9" s="0" t="n">
         <v>2000001004</v>
       </c>
@@ -1326,6 +1356,11 @@
       <c r="A10" s="0" t="n">
         <v>2000002001</v>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
+        </is>
+      </c>
       <c r="D10" s="0" t="n">
         <v>1</v>
       </c>
@@ -1348,6 +1383,11 @@
       <c r="A11" s="0" t="n">
         <v>2000002002</v>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
+        </is>
+      </c>
       <c r="C11" s="0" t="n">
         <v>2000002001</v>
       </c>
@@ -1375,6 +1415,11 @@
       <c r="A12" s="0" t="n">
         <v>2000002003</v>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
+        </is>
+      </c>
       <c r="C12" s="0" t="n">
         <v>2000002002</v>
       </c>
@@ -1402,6 +1447,11 @@
       <c r="A13" s="0" t="n">
         <v>2000002004</v>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
+        </is>
+      </c>
       <c r="C13" s="0" t="n">
         <v>2000002003</v>
       </c>
@@ -1429,6 +1479,11 @@
       <c r="A14" s="0" t="n">
         <v>2000002005</v>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
+        </is>
+      </c>
       <c r="C14" s="0" t="n">
         <v>2000002004</v>
       </c>
@@ -1456,6 +1511,11 @@
       <c r="A15" s="0" t="n">
         <v>2000003001</v>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
+        </is>
+      </c>
       <c r="D15" s="0" t="n">
         <v>1</v>
       </c>
@@ -1478,6 +1538,11 @@
       <c r="A16" s="0" t="n">
         <v>2000003002</v>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
+        </is>
+      </c>
       <c r="C16" s="0" t="n">
         <v>2000003001</v>
       </c>
@@ -1505,6 +1570,11 @@
       <c r="A17" s="0" t="n">
         <v>2000003003</v>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
+        </is>
+      </c>
       <c r="C17" s="0" t="n">
         <v>2000003002</v>
       </c>
@@ -1532,6 +1602,11 @@
       <c r="A18" s="0" t="n">
         <v>2000003004</v>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
+        </is>
+      </c>
       <c r="C18" s="0" t="n">
         <v>2000003003</v>
       </c>
@@ -1559,6 +1634,11 @@
       <c r="A19" s="0" t="n">
         <v>2000003005</v>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
+        </is>
+      </c>
       <c r="C19" s="0" t="n">
         <v>2000003004</v>
       </c>
@@ -1586,6 +1666,11 @@
       <c r="A20" s="0" t="n">
         <v>2000004001</v>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>abyssal_damage</t>
+        </is>
+      </c>
       <c r="D20" s="0" t="n">
         <v>1</v>
       </c>
@@ -1610,6 +1695,11 @@
       <c r="A21" s="0" t="n">
         <v>2000004002</v>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>abyssal_damage</t>
+        </is>
+      </c>
       <c r="C21" s="0" t="n">
         <v>2000004001</v>
       </c>
@@ -1637,6 +1727,11 @@
       <c r="A22" s="0" t="n">
         <v>2000004003</v>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>abyssal_damage</t>
+        </is>
+      </c>
       <c r="C22" s="0" t="n">
         <v>2000004002</v>
       </c>
@@ -1664,6 +1759,11 @@
       <c r="A23" s="0" t="n">
         <v>2000004004</v>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>abyssal_damage</t>
+        </is>
+      </c>
       <c r="C23" s="0" t="n">
         <v>2000004003</v>
       </c>
@@ -1691,6 +1791,11 @@
       <c r="A24" s="0" t="n">
         <v>2000004005</v>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>abyssal_damage</t>
+        </is>
+      </c>
       <c r="C24" s="0" t="n">
         <v>2000004004</v>
       </c>
@@ -1715,135 +1820,160 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="0" t="n">
         <v>2000005001</v>
       </c>
-      <c r="C25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>abyssal_slow</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>3000600001</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="0" t="n">
         <v>2000005001</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="0" t="n">
         <v>2000005001</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="0" t="n">
         <v>2000005002</v>
       </c>
-      <c r="C26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>abyssal_slow</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n">
         <v>2000005001</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>3000600002</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="0" t="n">
         <v>2000005002</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="0" t="n">
         <v>2000005002</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="0" t="n">
         <v>2000005003</v>
       </c>
-      <c r="C27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>abyssal_slow</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n">
         <v>2000005002</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>3000600003</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="0" t="n">
         <v>2000005003</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="0" t="n">
         <v>2000005003</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="0" t="n">
         <v>2000005004</v>
       </c>
-      <c r="C28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>abyssal_slow</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n">
         <v>2000005003</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>3000600004</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="0" t="n">
         <v>2000005004</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="0" t="n">
         <v>2000005004</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="0" t="n">
         <v>2000005005</v>
       </c>
-      <c r="C29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>abyssal_slow</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="n">
         <v>2000005004</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>3000600005</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="0" t="n">
         <v>2000005005</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="0" t="n">
         <v>2000005005</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1182,7 +1182,7 @@
       <c r="A4" s="0" t="n">
         <v>1000001001</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>abyssal_proliferation</t>
         </is>
@@ -1209,7 +1209,7 @@
       <c r="A5" s="0" t="n">
         <v>2000001001</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>abyssal_money</t>
         </is>
@@ -1236,7 +1236,7 @@
       <c r="A6" s="0" t="n">
         <v>2000001002</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>abyssal_money</t>
         </is>
@@ -1266,7 +1266,7 @@
       <c r="A7" s="0" t="n">
         <v>2000001003</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>abyssal_money</t>
         </is>
@@ -1296,7 +1296,7 @@
       <c r="A8" s="0" t="n">
         <v>2000001004</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>abyssal_money</t>
         </is>
@@ -1326,7 +1326,7 @@
       <c r="A9" s="0" t="n">
         <v>2000001005</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>abyssal_money</t>
         </is>
@@ -1356,9 +1356,9 @@
       <c r="A10" s="0" t="n">
         <v>2000002001</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>abyssal_hourglass</t>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
         </is>
       </c>
       <c r="D10" s="0" t="n">
@@ -1383,9 +1383,9 @@
       <c r="A11" s="0" t="n">
         <v>2000002002</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>abyssal_hourglass</t>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">
@@ -1415,9 +1415,9 @@
       <c r="A12" s="0" t="n">
         <v>2000002003</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>abyssal_hourglass</t>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
         </is>
       </c>
       <c r="C12" s="0" t="n">
@@ -1447,9 +1447,9 @@
       <c r="A13" s="0" t="n">
         <v>2000002004</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>abyssal_hourglass</t>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
@@ -1479,9 +1479,9 @@
       <c r="A14" s="0" t="n">
         <v>2000002005</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>abyssal_hourglass</t>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_fitness</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
@@ -1511,9 +1511,9 @@
       <c r="A15" s="0" t="n">
         <v>2000003001</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>abyssal_fitness</t>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
         </is>
       </c>
       <c r="D15" s="0" t="n">
@@ -1538,9 +1538,9 @@
       <c r="A16" s="0" t="n">
         <v>2000003002</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>abyssal_fitness</t>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
@@ -1570,9 +1570,9 @@
       <c r="A17" s="0" t="n">
         <v>2000003003</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>abyssal_fitness</t>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
@@ -1602,9 +1602,9 @@
       <c r="A18" s="0" t="n">
         <v>2000003004</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>abyssal_fitness</t>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
@@ -1634,9 +1634,9 @@
       <c r="A19" s="0" t="n">
         <v>2000003005</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>abyssal_fitness</t>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>abyssal_hourglass</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
@@ -1666,7 +1666,7 @@
       <c r="A20" s="0" t="n">
         <v>2000004001</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>abyssal_damage</t>
         </is>
@@ -1695,7 +1695,7 @@
       <c r="A21" s="0" t="n">
         <v>2000004002</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>abyssal_damage</t>
         </is>
@@ -1727,7 +1727,7 @@
       <c r="A22" s="0" t="n">
         <v>2000004003</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>abyssal_damage</t>
         </is>
@@ -1759,7 +1759,7 @@
       <c r="A23" s="0" t="n">
         <v>2000004004</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>abyssal_damage</t>
         </is>
@@ -1791,7 +1791,7 @@
       <c r="A24" s="0" t="n">
         <v>2000004005</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>abyssal_damage</t>
         </is>
@@ -1823,7 +1823,7 @@
       <c r="A25" s="0" t="n">
         <v>2000005001</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>abyssal_slow</t>
         </is>
@@ -1855,7 +1855,7 @@
       <c r="A26" s="0" t="n">
         <v>2000005002</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>abyssal_slow</t>
         </is>
@@ -1887,7 +1887,7 @@
       <c r="A27" s="0" t="n">
         <v>2000005003</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>abyssal_slow</t>
         </is>
@@ -1919,7 +1919,7 @@
       <c r="A28" s="0" t="n">
         <v>2000005004</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>abyssal_slow</t>
         </is>
@@ -1951,7 +1951,7 @@
       <c r="A29" s="0" t="n">
         <v>2000005005</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>abyssal_slow</t>
         </is>
@@ -1979,12 +1979,326 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="1"/>
-    <row r="35" ht="15" customHeight="1" s="1"/>
-    <row r="36" ht="15" customHeight="1" s="1"/>
-    <row r="37" ht="15" customHeight="1" s="1"/>
-    <row r="38" ht="15" customHeight="1" s="1"/>
-    <row r="39" ht="15" customHeight="1" s="1"/>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>abyssal_speed</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3000700001</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>唯快不破LV1-所有魔物攻击速度增加10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>abyssal_speed</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3000700002</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>唯快不破LV2-所有魔物攻击速度增加20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>abyssal_speed</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3000700003</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>唯快不破LV3-所有魔物攻击速度增加30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>abyssal_speed</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3000700004</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>唯快不破LV4-所有魔物攻击速度增加40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="1">
+      <c r="A34" t="n">
+        <v>2000006005</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abyssal_speed</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3000700005</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2000006005</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2000006005</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>唯快不破LV5-所有魔物攻击速度增加50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="1">
+      <c r="A35" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abyssal_shield</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3000800001</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>坚不可摧LV1-所有魔物护甲增加10%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="1">
+      <c r="A36" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>abyssal_shield</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3000800002</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>坚不可摧LV2-所有魔物护甲增加20%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="1">
+      <c r="A37" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>abyssal_shield</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3000800003</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>坚不可摧LV3-所有魔物护甲增加30%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="1">
+      <c r="A38" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>abyssal_shield</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3000800004</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>坚不可摧LV4-所有魔物护甲增加40%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="1">
+      <c r="A39" t="n">
+        <v>2000007005</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>abyssal_shield</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3000800005</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2000007005</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2000007005</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>坚不可摧LV5-所有魔物护甲增加50%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
     <row r="40" ht="15" customHeight="1" s="1"/>
     <row r="41" ht="15" customHeight="1" s="1"/>
     <row r="42" ht="15" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1094,6 +1094,11 @@
           <t>remark</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1136,6 +1141,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1176,6 +1186,11 @@
       <c r="H3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>是否有效(0无效1有效)</t>
         </is>
       </c>
     </row>
@@ -1205,6 +1220,9 @@
           <t>增殖-随机复制一个已有的魔物</t>
         </is>
       </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
@@ -1235,6 +1253,9 @@
           <t>奖励多多-战斗通关获得的奖励数量+1</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
@@ -1265,6 +1286,9 @@
           <t>再来一瓶-战斗通关可选择的奖励次数+1</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
@@ -1292,6 +1316,9 @@
           <t>钱多多-每一次击杀有10%的概率多掉落一次魔晶</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
@@ -1322,6 +1349,9 @@
           <t>钱多多-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
@@ -1352,6 +1382,9 @@
           <t>钱多多-每一次击杀有30%的概率多掉落一次魔晶</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
@@ -1382,6 +1415,9 @@
           <t>钱多多-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
@@ -1412,6 +1448,9 @@
           <t>钱多多-每一次击杀有50%的概率多掉落一次魔晶</t>
         </is>
       </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
@@ -1439,6 +1478,9 @@
           <t>强身健体-所有魔物体力增加10%</t>
         </is>
       </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
@@ -1471,6 +1513,9 @@
           <t>强身健体-所有魔物体力增加20%</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
@@ -1503,6 +1548,9 @@
           <t>强身健体-所有魔物体力增加30%</t>
         </is>
       </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
@@ -1535,6 +1583,9 @@
           <t>强身健体-所有魔物体力增加40%</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
@@ -1567,6 +1618,9 @@
           <t>强身健体-所有魔物体力增加50%</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
@@ -1594,6 +1648,9 @@
           <t>时光沙漏-所有魔物召唤CD减少10%</t>
         </is>
       </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
@@ -1626,6 +1683,9 @@
           <t>时光沙漏-所有魔物召唤CD减少20%</t>
         </is>
       </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
@@ -1658,6 +1718,9 @@
           <t>时光沙漏-所有魔物召唤CD减少30%</t>
         </is>
       </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
@@ -1690,6 +1753,9 @@
           <t>时光沙漏-所有魔物召唤CD减少40%</t>
         </is>
       </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
@@ -1722,6 +1788,9 @@
           <t>时光沙漏-所有魔物召唤CD减少50%</t>
         </is>
       </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
@@ -1751,6 +1820,9 @@
           <t>伤害性极强LV1-所有魔物攻击力增加10%</t>
         </is>
       </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
@@ -1783,6 +1855,9 @@
           <t>伤害性极强LV2-所有魔物攻击力增加20%</t>
         </is>
       </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
@@ -1815,6 +1890,9 @@
           <t>伤害性极强LV3-所有魔物攻击力增加30%</t>
         </is>
       </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
@@ -1847,6 +1925,9 @@
           <t>伤害性极强LV4-所有魔物攻击力增加40%</t>
         </is>
       </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
@@ -1879,6 +1960,9 @@
           <t>伤害性极强LV5-所有魔物攻击力增加50%</t>
         </is>
       </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
@@ -1911,6 +1995,9 @@
           <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
         </is>
       </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
@@ -1943,6 +2030,9 @@
           <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
         </is>
       </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
@@ -1975,6 +2065,9 @@
           <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
         </is>
       </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
@@ -2007,6 +2100,9 @@
           <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
         </is>
       </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
@@ -2039,6 +2135,9 @@
           <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
         </is>
       </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
@@ -2071,6 +2170,9 @@
           <t>唯快不破LV1-所有魔物攻击速度增加10%</t>
         </is>
       </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
@@ -2103,6 +2205,9 @@
           <t>唯快不破LV2-所有魔物攻击速度增加20%</t>
         </is>
       </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
@@ -2135,6 +2240,9 @@
           <t>唯快不破LV3-所有魔物攻击速度增加30%</t>
         </is>
       </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
@@ -2167,6 +2275,9 @@
           <t>唯快不破LV4-所有魔物攻击速度增加40%</t>
         </is>
       </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
@@ -2199,6 +2310,9 @@
           <t>唯快不破LV5-所有魔物攻击速度增加50%</t>
         </is>
       </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
@@ -2231,6 +2345,9 @@
           <t>坚不可摧LV1-所有魔物护甲增加10%(无护甲则无加成)</t>
         </is>
       </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
@@ -2263,6 +2380,9 @@
           <t>坚不可摧LV2-所有魔物护甲增加20%(无护甲则无加成)</t>
         </is>
       </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
@@ -2295,6 +2415,9 @@
           <t>坚不可摧LV3-所有魔物护甲增加30%(无护甲则无加成)</t>
         </is>
       </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="1">
       <c r="A40" s="0" t="n">
@@ -2327,6 +2450,9 @@
           <t>坚不可摧LV4-所有魔物护甲增加40%(无护甲则无加成)</t>
         </is>
       </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="1">
       <c r="A41" s="0" t="n">
@@ -2358,6 +2484,9 @@
         <is>
           <t>坚不可摧LV5-所有魔物护甲增加50%(无护甲则无加成)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1094,7 +1094,7 @@
           <t>remark</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
@@ -1141,7 +1141,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1188,7 +1188,7 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>是否有效(0无效1有效)</t>
         </is>
@@ -1220,7 +1220,7 @@
           <t>增殖-随机复制一个已有的魔物</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
           <t>奖励多多-战斗通关获得的奖励数量+1</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1286,34 +1286,37 @@
           <t>再来一瓶-战斗通关可选择的奖励次数+1</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="n">
-        <v>2000001001</v>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>2000001001</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>2000001001</v>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有10%的概率多掉落一次魔晶</t>
+      <c r="A7" t="n">
+        <v>1000004001</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_11</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3001100001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1000004001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000004001</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>大力出奇迹-随机一只防守魔物攻击力翻倍(单级可重复)</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1321,32 +1324,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="n">
-        <v>2000001002</v>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>2000001001</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="0" t="n">
-        <v>3000200002</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>2000001002</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>2000001002</v>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有20%的概率多掉落一次魔晶</t>
+      <c r="A8" t="n">
+        <v>1000005001</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_12</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1000005001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000005001</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>膘肥体壮-随机一只防守魔物生命翻倍(单级可重复)</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1354,32 +1357,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="n">
-        <v>2000001003</v>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>2000001002</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="0" t="n">
-        <v>3000200003</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>2000001003</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>2000001003</v>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有30%的概率多掉落一次魔晶</t>
+      <c r="A9" t="n">
+        <v>1000006001</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_13</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3001300001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1000006001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000006001</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>钢铁憨憨-随机一只防守魔物护甲翻倍(单级可重复)</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1387,32 +1390,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="n">
-        <v>2000001004</v>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>2000001003</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="0" t="n">
-        <v>3000200004</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>2000001004</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>2000001004</v>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有40%的概率多掉落一次魔晶</t>
+      <c r="A10" t="n">
+        <v>1000007001</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_14</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3001400001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1000007001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000007001</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>急性子-随机一只防守魔物攻击翻倍快(单级可重复)</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1421,692 +1424,681 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>2000001005</v>
+        <v>2000001001</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_9</t>
         </is>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>2000001004</v>
-      </c>
       <c r="D11" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>3000200005</v>
+        <v>3000200001</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>2000001005</v>
+        <v>2000001001</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>2000001005</v>
+        <v>2000001001</v>
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>钱多多-每一次击杀有50%的概率多掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+          <t>钱多多-每一次击杀有10%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>2000002001</v>
+        <v>2000001002</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_2</t>
-        </is>
+          <t>ui_abyssalblessing_9</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>2000001001</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200002</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>2000002001</v>
+        <v>2000001002</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>2000002001</v>
+        <v>2000001002</v>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>强身健体-所有魔物体力增加10%</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+          <t>钱多多-每一次击杀有20%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>2000002002</v>
+        <v>2000001003</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_2</t>
+          <t>ui_abyssalblessing_9</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
-        <v>2000002001</v>
+        <v>2000001002</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3000300002</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>3000200003</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>2000002002</v>
+        <v>2000001003</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>2000002002</v>
+        <v>2000001003</v>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>强身健体-所有魔物体力增加20%</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+          <t>钱多多-每一次击杀有30%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>2000002003</v>
+        <v>2000001004</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_2</t>
+          <t>ui_abyssalblessing_9</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
-        <v>2000002002</v>
+        <v>2000001003</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3000300003</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>3000200004</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>2000002003</v>
+        <v>2000001004</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>2000002003</v>
+        <v>2000001004</v>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>强身健体-所有魔物体力增加30%</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+          <t>钱多多-每一次击杀有40%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>2000002004</v>
+        <v>2000001005</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_2</t>
+          <t>ui_abyssalblessing_9</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
-        <v>2000002003</v>
+        <v>2000001004</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3000300004</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>3000200005</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>2000002004</v>
+        <v>2000001005</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>2000002004</v>
+        <v>2000001005</v>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>强身健体-所有魔物体力增加40%</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+          <t>钱多多-每一次击杀有50%的概率多掉落一次魔晶</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>2000002005</v>
+        <v>2000002001</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_2</t>
         </is>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>2000002004</v>
-      </c>
       <c r="D16" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3000300005</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>3000300001</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>2000002005</v>
+        <v>2000002001</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>2000002005</v>
+        <v>2000002001</v>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>强身健体-所有魔物体力增加50%</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+          <t>强身健体-所有魔物体力增加10%</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>2000003001</v>
+        <v>2000002002</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_8</t>
-        </is>
+          <t>ui_abyssalblessing_2</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>2000002001</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>3000400001</v>
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3000300002</t>
+        </is>
       </c>
       <c r="F17" s="0" t="n">
-        <v>2000003001</v>
+        <v>2000002002</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>2000003001</v>
+        <v>2000002002</v>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏-所有魔物召唤CD减少10%</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+          <t>强身健体-所有魔物体力增加20%</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>2000003002</v>
+        <v>2000002003</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_8</t>
+          <t>ui_abyssalblessing_2</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
-        <v>2000003001</v>
+        <v>2000002002</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3000400002</t>
+          <t>3000300003</t>
         </is>
       </c>
       <c r="F18" s="0" t="n">
-        <v>2000003002</v>
+        <v>2000002003</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>2000003002</v>
+        <v>2000002003</v>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏-所有魔物召唤CD减少20%</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+          <t>强身健体-所有魔物体力增加30%</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>2000003003</v>
+        <v>2000002004</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_8</t>
+          <t>ui_abyssalblessing_2</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
-        <v>2000003002</v>
+        <v>2000002003</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3000400003</t>
+          <t>3000300004</t>
         </is>
       </c>
       <c r="F19" s="0" t="n">
-        <v>2000003003</v>
+        <v>2000002004</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>2000003003</v>
+        <v>2000002004</v>
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏-所有魔物召唤CD减少30%</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+          <t>强身健体-所有魔物体力增加40%</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>2000003004</v>
+        <v>2000002005</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_8</t>
+          <t>ui_abyssalblessing_2</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
-        <v>2000003003</v>
+        <v>2000002004</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3000400004</t>
+          <t>3000300005</t>
         </is>
       </c>
       <c r="F20" s="0" t="n">
-        <v>2000003004</v>
+        <v>2000002005</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>2000003004</v>
+        <v>2000002005</v>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏-所有魔物召唤CD减少40%</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+          <t>强身健体-所有魔物体力增加50%</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>2000003005</v>
+        <v>2000003001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_8</t>
         </is>
       </c>
-      <c r="C21" s="0" t="n">
-        <v>2000003004</v>
-      </c>
       <c r="D21" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>3000400005</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>3000400001</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>2000003005</v>
+        <v>2000003001</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>2000003005</v>
+        <v>2000003001</v>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏-所有魔物召唤CD减少50%</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+          <t>时光沙漏-所有魔物召唤CD减少10%</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>2000004001</v>
+        <v>2000003002</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_4</t>
-        </is>
+          <t>ui_abyssalblessing_8</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>2000003001</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>3000500001</t>
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3000400002</t>
         </is>
       </c>
       <c r="F22" s="0" t="n">
-        <v>2000004001</v>
+        <v>2000003002</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>2000004001</v>
+        <v>2000003002</v>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强LV1-所有魔物攻击力增加10%</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+          <t>时光沙漏-所有魔物召唤CD减少20%</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>2000004002</v>
+        <v>2000003003</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_4</t>
+          <t>ui_abyssalblessing_8</t>
         </is>
       </c>
       <c r="C23" s="0" t="n">
-        <v>2000004001</v>
+        <v>2000003002</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>3000500002</t>
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3000400003</t>
         </is>
       </c>
       <c r="F23" s="0" t="n">
-        <v>2000004002</v>
+        <v>2000003003</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>2000004002</v>
+        <v>2000003003</v>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强LV2-所有魔物攻击力增加20%</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+          <t>时光沙漏-所有魔物召唤CD减少30%</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>2000004003</v>
+        <v>2000003004</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_4</t>
+          <t>ui_abyssalblessing_8</t>
         </is>
       </c>
       <c r="C24" s="0" t="n">
-        <v>2000004002</v>
+        <v>2000003003</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>3000500003</t>
+        <v>4</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3000400004</t>
         </is>
       </c>
       <c r="F24" s="0" t="n">
-        <v>2000004003</v>
+        <v>2000003004</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>2000004003</v>
+        <v>2000003004</v>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强LV3-所有魔物攻击力增加30%</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+          <t>时光沙漏-所有魔物召唤CD减少40%</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>2000004004</v>
+        <v>2000003005</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_4</t>
+          <t>ui_abyssalblessing_8</t>
         </is>
       </c>
       <c r="C25" s="0" t="n">
-        <v>2000004003</v>
+        <v>2000003004</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t>3000500004</t>
+        <v>5</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3000400005</t>
         </is>
       </c>
       <c r="F25" s="0" t="n">
-        <v>2000004004</v>
+        <v>2000003005</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>2000004004</v>
+        <v>2000003005</v>
       </c>
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强LV4-所有魔物攻击力增加40%</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+          <t>时光沙漏-所有魔物召唤CD减少50%</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>2000004005</v>
+        <v>2000004001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_4</t>
         </is>
       </c>
-      <c r="C26" s="0" t="n">
-        <v>2000004004</v>
-      </c>
       <c r="D26" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>3000500005</t>
+          <t>3000500001</t>
         </is>
       </c>
       <c r="F26" s="0" t="n">
-        <v>2000004005</v>
+        <v>2000004001</v>
       </c>
       <c r="G26" s="0" t="n">
-        <v>2000004005</v>
+        <v>2000004001</v>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强LV5-所有魔物攻击力增加50%</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+          <t>伤害性极强LV1-所有魔物攻击力增加10%</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>2000005001</v>
+        <v>2000004002</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_5</t>
+          <t>ui_abyssalblessing_4</t>
         </is>
       </c>
       <c r="C27" s="0" t="n">
-        <v>0</v>
+        <v>2000004001</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>3000600001</t>
+          <t>3000500002</t>
         </is>
       </c>
       <c r="F27" s="0" t="n">
-        <v>2000005001</v>
+        <v>2000004002</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>2000005001</v>
+        <v>2000004002</v>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+          <t>伤害性极强LV2-所有魔物攻击力增加20%</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>2000005002</v>
+        <v>2000004003</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_5</t>
+          <t>ui_abyssalblessing_4</t>
         </is>
       </c>
       <c r="C28" s="0" t="n">
-        <v>2000005001</v>
+        <v>2000004002</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>3000600002</t>
+          <t>3000500003</t>
         </is>
       </c>
       <c r="F28" s="0" t="n">
-        <v>2000005002</v>
+        <v>2000004003</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>2000005002</v>
+        <v>2000004003</v>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+          <t>伤害性极强LV3-所有魔物攻击力增加30%</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>2000005003</v>
+        <v>2000004004</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_5</t>
+          <t>ui_abyssalblessing_4</t>
         </is>
       </c>
       <c r="C29" s="0" t="n">
-        <v>2000005002</v>
+        <v>2000004003</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>3000600003</t>
+          <t>3000500004</t>
         </is>
       </c>
       <c r="F29" s="0" t="n">
-        <v>2000005003</v>
+        <v>2000004004</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>2000005003</v>
+        <v>2000004004</v>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+          <t>伤害性极强LV4-所有魔物攻击力增加40%</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>2000005004</v>
+        <v>2000004005</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_5</t>
+          <t>ui_abyssalblessing_4</t>
         </is>
       </c>
       <c r="C30" s="0" t="n">
-        <v>2000005003</v>
+        <v>2000004004</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>3000600004</t>
+          <t>3000500005</t>
         </is>
       </c>
       <c r="F30" s="0" t="n">
-        <v>2000005004</v>
+        <v>2000004005</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>2000005004</v>
+        <v>2000004005</v>
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+          <t>伤害性极强LV5-所有魔物攻击力增加50%</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>2000005005</v>
+        <v>2000005001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
@@ -2114,174 +2106,174 @@
         </is>
       </c>
       <c r="C31" s="0" t="n">
-        <v>2000005004</v>
+        <v>0</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>3000600005</t>
+          <t>3000600001</t>
         </is>
       </c>
       <c r="F31" s="0" t="n">
-        <v>2000005005</v>
+        <v>2000005001</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>2000005005</v>
+        <v>2000005001</v>
       </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+          <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>2000006001</v>
+        <v>2000005002</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_3</t>
+          <t>ui_abyssalblessing_5</t>
         </is>
       </c>
       <c r="C32" s="0" t="n">
-        <v>0</v>
+        <v>2000005001</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>3000700001</t>
+          <t>3000600002</t>
         </is>
       </c>
       <c r="F32" s="0" t="n">
-        <v>2000006001</v>
+        <v>2000005002</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>2000006001</v>
+        <v>2000005002</v>
       </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>唯快不破LV1-所有魔物攻击速度增加10%</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+          <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>2000006002</v>
+        <v>2000005003</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_3</t>
+          <t>ui_abyssalblessing_5</t>
         </is>
       </c>
       <c r="C33" s="0" t="n">
-        <v>2000006001</v>
+        <v>2000005002</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>3000700002</t>
+          <t>3000600003</t>
         </is>
       </c>
       <c r="F33" s="0" t="n">
-        <v>2000006002</v>
+        <v>2000005003</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>2000006002</v>
+        <v>2000005003</v>
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>唯快不破LV2-所有魔物攻击速度增加20%</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+          <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>2000006003</v>
+        <v>2000005004</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_3</t>
+          <t>ui_abyssalblessing_5</t>
         </is>
       </c>
       <c r="C34" s="0" t="n">
-        <v>2000006002</v>
+        <v>2000005003</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>3000700003</t>
+          <t>3000600004</t>
         </is>
       </c>
       <c r="F34" s="0" t="n">
-        <v>2000006003</v>
+        <v>2000005004</v>
       </c>
       <c r="G34" s="0" t="n">
-        <v>2000006003</v>
+        <v>2000005004</v>
       </c>
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>唯快不破LV3-所有魔物攻击速度增加30%</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+          <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>2000006004</v>
+        <v>2000005005</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_3</t>
+          <t>ui_abyssalblessing_5</t>
         </is>
       </c>
       <c r="C35" s="0" t="n">
-        <v>2000006003</v>
+        <v>2000005004</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>3000700004</t>
+          <t>3000600005</t>
         </is>
       </c>
       <c r="F35" s="0" t="n">
-        <v>2000006004</v>
+        <v>2000005005</v>
       </c>
       <c r="G35" s="0" t="n">
-        <v>2000006004</v>
+        <v>2000005005</v>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>唯快不破LV4-所有魔物攻击速度增加40%</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
+          <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>2000006005</v>
+        <v>2000006001</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
@@ -2289,209 +2281,346 @@
         </is>
       </c>
       <c r="C36" s="0" t="n">
-        <v>2000006004</v>
+        <v>0</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>3000700005</t>
+          <t>3000700001</t>
         </is>
       </c>
       <c r="F36" s="0" t="n">
-        <v>2000006005</v>
+        <v>2000006001</v>
       </c>
       <c r="G36" s="0" t="n">
-        <v>2000006005</v>
+        <v>2000006001</v>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>唯快不破LV5-所有魔物攻击速度增加50%</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
+          <t>唯快不破LV1-所有魔物攻击速度增加10%</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>2000007001</v>
+        <v>2000006002</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_1</t>
+          <t>ui_abyssalblessing_3</t>
         </is>
       </c>
       <c r="C37" s="0" t="n">
-        <v>0</v>
+        <v>2000006001</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>3000800001</t>
+          <t>3000700002</t>
         </is>
       </c>
       <c r="F37" s="0" t="n">
-        <v>2000007001</v>
+        <v>2000006002</v>
       </c>
       <c r="G37" s="0" t="n">
-        <v>2000007001</v>
+        <v>2000006002</v>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>坚不可摧LV1-所有魔物护甲增加10%(无护甲则无加成)</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+          <t>唯快不破LV2-所有魔物攻击速度增加20%</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>2000007002</v>
+        <v>2000006003</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_1</t>
+          <t>ui_abyssalblessing_3</t>
         </is>
       </c>
       <c r="C38" s="0" t="n">
-        <v>2000007001</v>
+        <v>2000006002</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>3000800002</t>
+          <t>3000700003</t>
         </is>
       </c>
       <c r="F38" s="0" t="n">
-        <v>2000007002</v>
+        <v>2000006003</v>
       </c>
       <c r="G38" s="0" t="n">
-        <v>2000007002</v>
+        <v>2000006003</v>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>坚不可摧LV2-所有魔物护甲增加20%(无护甲则无加成)</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
+          <t>唯快不破LV3-所有魔物攻击速度增加30%</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>2000007003</v>
+        <v>2000006004</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_1</t>
+          <t>ui_abyssalblessing_3</t>
         </is>
       </c>
       <c r="C39" s="0" t="n">
-        <v>2000007002</v>
+        <v>2000006003</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>3000800003</t>
+          <t>3000700004</t>
         </is>
       </c>
       <c r="F39" s="0" t="n">
-        <v>2000007003</v>
+        <v>2000006004</v>
       </c>
       <c r="G39" s="0" t="n">
-        <v>2000007003</v>
+        <v>2000006004</v>
       </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>坚不可摧LV3-所有魔物护甲增加30%(无护甲则无加成)</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
+          <t>唯快不破LV4-所有魔物攻击速度增加40%</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="1">
       <c r="A40" s="0" t="n">
-        <v>2000007004</v>
+        <v>2000006005</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>ui_abyssalblessing_1</t>
+          <t>ui_abyssalblessing_3</t>
         </is>
       </c>
       <c r="C40" s="0" t="n">
-        <v>2000007003</v>
+        <v>2000006004</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>3000800004</t>
+          <t>3000700005</t>
         </is>
       </c>
       <c r="F40" s="0" t="n">
-        <v>2000007004</v>
+        <v>2000006005</v>
       </c>
       <c r="G40" s="0" t="n">
-        <v>2000007004</v>
+        <v>2000006005</v>
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>坚不可摧LV4-所有魔物护甲增加40%(无护甲则无加成)</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
+          <t>唯快不破LV5-所有魔物攻击速度增加50%</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="1">
       <c r="A41" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_1</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>3000800001</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧LV1-所有魔物护甲增加10%(无护甲则无加成)</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="1">
+      <c r="A42" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_1</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>3000800002</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧LV2-所有魔物护甲增加20%(无护甲则无加成)</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="1">
+      <c r="A43" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_1</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>3000800003</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧LV3-所有魔物护甲增加30%(无护甲则无加成)</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="1">
+      <c r="A44" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_1</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>3000800004</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧LV4-所有魔物护甲增加40%(无护甲则无加成)</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="n">
         <v>2000007005</v>
       </c>
-      <c r="B41" s="0" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_1</t>
         </is>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C45" s="0" t="n">
         <v>2000007004</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D45" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E41" s="0" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>3000800005</t>
         </is>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F45" s="0" t="n">
         <v>2000007005</v>
       </c>
-      <c r="G41" s="0" t="n">
+      <c r="G45" s="0" t="n">
         <v>2000007005</v>
       </c>
-      <c r="H41" s="0" t="inlineStr">
+      <c r="H45" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV5-所有魔物护甲增加50%(无护甲则无加成)</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="1"/>
-    <row r="43" ht="15" customHeight="1" s="1"/>
-    <row r="44" ht="15" customHeight="1" s="1"/>
+      <c r="I45" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="76" ht="12" customHeight="1" s="1"/>
     <row r="77" ht="12" customHeight="1" s="1"/>
     <row r="78" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1291,134 +1291,134 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>1000004001</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_11</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>3001100001</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>1000004001</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>1000004001</v>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>大力出奇迹-随机一只防守魔物攻击力翻倍(单级不可重复)</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="n">
+        <v>1000005001</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_12</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>3001100001</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1000004001</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1000004001</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>大力出奇迹-随机一只防守魔物攻击力翻倍(单级可重复)</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="D8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="F8" s="0" t="n">
         <v>1000005001</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_12</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="G8" s="0" t="n">
+        <v>1000005001</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>膘肥体壮-随机一只防守魔物生命翻倍(单级不可重复)</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n">
+        <v>1000006001</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_13</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>3001300001</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>1000006001</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>1000006001</v>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>钢铁憨憨-随机一只防守魔物护甲翻倍(单级不可重复)</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
+        <v>1000007001</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_14</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>3001200001</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1000005001</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1000005001</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>膘肥体壮-随机一只防守魔物生命翻倍(单级可重复)</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1000006001</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_13</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3001300001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1000006001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1000006001</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>钢铁憨憨-随机一只防守魔物护甲翻倍(单级可重复)</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="D10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>3001400001</v>
+      </c>
+      <c r="F10" s="0" t="n">
         <v>1000007001</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_14</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3001400001</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="G10" s="0" t="n">
         <v>1000007001</v>
       </c>
-      <c r="G10" t="n">
-        <v>1000007001</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>急性子-随机一只防守魔物攻击翻倍快(单级可重复)</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>急性子-随机一只防守魔物攻击翻倍快(单级不可重复)</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1099,6 +1099,11 @@
           <t>valid</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1146,6 +1151,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1191,6 +1201,11 @@
       <c r="I3" s="0" t="inlineStr">
         <is>
           <t>是否有效(0无效1有效)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>一局最多可获得次数(0=不限)</t>
         </is>
       </c>
     </row>
@@ -1223,6 +1238,9 @@
       <c r="I4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
@@ -1256,6 +1274,9 @@
       <c r="I5" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
@@ -1289,6 +1310,9 @@
       <c r="I6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
@@ -1303,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>3001100001</v>
@@ -1316,10 +1340,13 @@
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>大力出奇迹-随机一只防守魔物攻击力翻倍(单级不可重复)</t>
+          <t>大力出奇迹-随机一只防守魔物攻击力翻倍(一局限1次)</t>
         </is>
       </c>
       <c r="I7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1336,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>3001200001</v>
@@ -1349,10 +1376,13 @@
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>膘肥体壮-随机一只防守魔物生命翻倍(单级不可重复)</t>
+          <t>膘肥体壮-随机一只防守魔物生命翻倍(一局限1次)</t>
         </is>
       </c>
       <c r="I8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1369,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>3001300001</v>
@@ -1382,10 +1412,13 @@
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>钢铁憨憨-随机一只防守魔物护甲翻倍(单级不可重复)</t>
+          <t>钢铁憨憨-随机一只防守魔物护甲翻倍(一局限1次)</t>
         </is>
       </c>
       <c r="I9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1402,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>3001400001</v>
@@ -1415,10 +1448,13 @@
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>急性子-随机一只防守魔物攻击翻倍快(单级不可重复)</t>
+          <t>急性子-随机一只防守魔物攻击翻倍快(一局限1次)</t>
         </is>
       </c>
       <c r="I10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1451,6 +1487,9 @@
       <c r="I11" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
@@ -1484,6 +1523,9 @@
       <c r="I12" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
@@ -1517,6 +1559,9 @@
       <c r="I13" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
@@ -1550,6 +1595,9 @@
       <c r="I14" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
@@ -1583,6 +1631,9 @@
       <c r="I15" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
@@ -1613,6 +1664,9 @@
       <c r="I16" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
@@ -1648,6 +1702,9 @@
       <c r="I17" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
@@ -1683,6 +1740,9 @@
       <c r="I18" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
@@ -1718,6 +1778,9 @@
       <c r="I19" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
@@ -1753,6 +1816,9 @@
       <c r="I20" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
@@ -1783,6 +1849,9 @@
       <c r="I21" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
@@ -1818,6 +1887,9 @@
       <c r="I22" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
@@ -1853,6 +1925,9 @@
       <c r="I23" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
@@ -1888,6 +1963,9 @@
       <c r="I24" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
@@ -1923,6 +2001,9 @@
       <c r="I25" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
@@ -1955,6 +2036,9 @@
       <c r="I26" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
@@ -1990,6 +2074,9 @@
       <c r="I27" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
@@ -2025,6 +2112,9 @@
       <c r="I28" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
@@ -2060,6 +2150,9 @@
       <c r="I29" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
@@ -2095,6 +2188,9 @@
       <c r="I30" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
@@ -2130,6 +2226,9 @@
       <c r="I31" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
@@ -2165,6 +2264,9 @@
       <c r="I32" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
@@ -2200,6 +2302,9 @@
       <c r="I33" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
@@ -2235,6 +2340,9 @@
       <c r="I34" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
@@ -2270,6 +2378,9 @@
       <c r="I35" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
@@ -2305,6 +2416,9 @@
       <c r="I36" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
@@ -2340,6 +2454,9 @@
       <c r="I37" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
@@ -2375,6 +2492,9 @@
       <c r="I38" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
@@ -2410,6 +2530,9 @@
       <c r="I39" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="1">
       <c r="A40" s="0" t="n">
@@ -2445,6 +2568,9 @@
       <c r="I40" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="1">
       <c r="A41" s="0" t="n">
@@ -2480,6 +2606,9 @@
       <c r="I41" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="1">
       <c r="A42" s="0" t="n">
@@ -2515,6 +2644,9 @@
       <c r="I42" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="1">
       <c r="A43" s="0" t="n">
@@ -2550,6 +2682,9 @@
       <c r="I43" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="1">
       <c r="A44" s="0" t="n">
@@ -2585,6 +2720,9 @@
       <c r="I44" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
@@ -2619,6 +2757,9 @@
       </c>
       <c r="I45" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1099,7 +1099,7 @@
           <t>valid</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>max_count</t>
         </is>
@@ -1151,7 +1151,7 @@
           <t>int</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1203,7 +1203,7 @@
           <t>是否有效(0无效1有效)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>一局最多可获得次数(0=不限)</t>
         </is>
@@ -1238,7 +1238,7 @@
       <c r="I4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       <c r="I5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       <c r="I6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       <c r="I7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       <c r="I8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="I9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       <c r="I10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       <c r="I11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       <c r="I12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       <c r="I13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       <c r="I14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       <c r="I15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       <c r="I16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       <c r="I17" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       <c r="I18" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       <c r="I19" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       <c r="I20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       <c r="I21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       <c r="I22" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       <c r="I23" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       <c r="I24" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       <c r="I25" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       <c r="I26" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       <c r="I27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       <c r="I28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="I29" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       <c r="I30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       <c r="I31" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       <c r="I32" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       <c r="I33" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       <c r="I34" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
       <c r="I35" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       <c r="I36" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       <c r="I37" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       <c r="I38" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       <c r="I39" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       <c r="I40" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       <c r="I41" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       <c r="I42" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       <c r="I43" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       <c r="I44" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2758,7 +2758,1147 @@
       <c r="I45" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_120</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3001500001</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.1-每只1%(动态)</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_120</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3001500002</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.2-每只2%(动态)</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_120</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3001500003</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.3-每只3%(动态)</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_120</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3001500004</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.4-每只4%(动态)</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2000008005</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_120</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3001500005</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2000008005</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2000008005</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.5-每只5%(动态)</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_121</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3001600001</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.1-每只1%(动态)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_121</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3001600002</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.2-每只2%(动态)</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_121</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3001600003</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.3-每只3%(动态)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_121</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3001600004</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.4-每只4%(动态)</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2000009005</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_121</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3001600005</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2000009005</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2000009005</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.5-每只5%(动态)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2000010001</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_122</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3001700001</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2000010001</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2000010001</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.1-每只1%(动态)</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2000010002</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_122</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2000010001</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3001700002</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>2000010002</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2000010002</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.2-每只2%(动态)</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2000010003</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_122</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2000010002</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3001700003</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2000010003</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2000010003</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.3-每只3%(动态)</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2000010004</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_122</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2000010003</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>3001700004</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2000010004</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2000010004</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.4-每只4%(动态)</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2000010005</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_122</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2000010004</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3001700005</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2000010005</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2000010005</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.5-每只5%(动态)</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2000011001</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_123</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3001800001</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>2000011001</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2000011001</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.1-每只1%(动态)</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2000011002</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_123</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2000011001</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3001800002</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2000011002</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2000011002</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.2-每只2%(动态)</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2000011003</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_123</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2000011002</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3001800003</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2000011003</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2000011003</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.3-每只3%(动态)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2000011004</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_123</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2000011003</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3001800004</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2000011004</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2000011004</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.4-每只4%(动态)</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2000011005</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_123</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2000011004</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3001800005</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2000011005</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2000011005</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.5-每只5%(动态)</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2000012001</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_124</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3001900001</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2000012001</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2000012001</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.1-每只1%(动态)</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2000012002</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_124</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2000012001</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3001900002</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2000012002</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2000012002</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.2-每只2%(动态)</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2000012003</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_124</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2000012002</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3001900003</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2000012003</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2000012003</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.3-每只3%(动态)</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2000012004</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_124</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2000012003</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3001900004</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2000012004</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2000012004</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.4-每只4%(动态)</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2000012005</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_124</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2000012004</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>3001900005</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2000012005</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2000012005</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.5-每只5%(动态)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2000013001</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_125</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3002000001</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>2000013001</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2000013001</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.1-每只1%(动态)</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2000013002</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_125</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2000013001</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3002000002</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>2000013002</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2000013002</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.2-每只2%(动态)</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2000013003</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_125</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2000013002</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3002000003</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>2000013003</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2000013003</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.3-每只3%(动态)</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2000013004</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_125</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2000013003</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>3002000004</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>2000013004</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2000013004</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.4-每只4%(动态)</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2000013005</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_125</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2000013004</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3002000005</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>2000013005</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2000013005</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.5-每只5%(动态)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1481,7 +1481,7 @@
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>钱多多-每一次击杀有10%的概率多掉落一次魔晶</t>
+          <t>钱多多-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="I11" s="0" t="n">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>钱多多-每一次击杀有20%的概率多掉落一次魔晶</t>
+          <t>钱多多-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="I12" s="0" t="n">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>钱多多-每一次击杀有30%的概率多掉落一次魔晶</t>
+          <t>钱多多-每一次击杀有60%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="I13" s="0" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>钱多多-每一次击杀有40%的概率多掉落一次魔晶</t>
+          <t>钱多多-每一次击杀有80%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="I14" s="0" t="n">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>钱多多-每一次击杀有50%的概率多掉落一次魔晶</t>
+          <t>钱多多-每一次击杀有100%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="I15" s="0" t="n">
@@ -2763,1142 +2763,1142 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="0" t="n">
         <v>2000008001</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_120</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="C46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>3001500001</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="0" t="n">
         <v>2000008001</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" s="0" t="n">
         <v>2000008001</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·攻击Lv.1-每只1%(动态)</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="I46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="0" t="n">
         <v>2000008002</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_120</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="0" t="n">
         <v>2000008001</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>3001500002</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="0" t="n">
         <v>2000008002</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="0" t="n">
         <v>2000008002</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·攻击Lv.2-每只2%(动态)</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="I47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="0" t="n">
         <v>2000008003</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_120</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="0" t="n">
         <v>2000008002</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>3001500003</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="0" t="n">
         <v>2000008003</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="0" t="n">
         <v>2000008003</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·攻击Lv.3-每只3%(动态)</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="I48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="0" t="n">
         <v>2000008004</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_120</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="0" t="n">
         <v>2000008003</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>3001500004</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="0" t="n">
         <v>2000008004</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="0" t="n">
         <v>2000008004</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·攻击Lv.4-每只4%(动态)</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="I49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="0" t="n">
         <v>2000008005</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_120</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="0" t="n">
         <v>2000008004</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>3001500005</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="0" t="n">
         <v>2000008005</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" s="0" t="n">
         <v>2000008005</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·攻击Lv.5-每只5%(动态)</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="I50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="0" t="n">
         <v>2000009001</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_121</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="C51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>3001600001</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="0" t="n">
         <v>2000009001</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" s="0" t="n">
         <v>2000009001</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·护甲Lv.1-每只1%(动态)</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
+      <c r="I51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="0" t="n">
         <v>2000009002</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_121</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="0" t="n">
         <v>2000009001</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>3001600002</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="0" t="n">
         <v>2000009002</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" s="0" t="n">
         <v>2000009002</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·护甲Lv.2-每只2%(动态)</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="n">
+      <c r="I52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="0" t="n">
         <v>2000009003</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_121</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="0" t="n">
         <v>2000009002</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>3001600003</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="0" t="n">
         <v>2000009003</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="0" t="n">
         <v>2000009003</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·护甲Lv.3-每只3%(动态)</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="I53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="0" t="n">
         <v>2000009004</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_121</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="0" t="n">
         <v>2000009003</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>3001600004</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="0" t="n">
         <v>2000009004</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" s="0" t="n">
         <v>2000009004</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·护甲Lv.4-每只4%(动态)</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="n">
+      <c r="I54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="0" t="n">
         <v>2000009005</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_121</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="0" t="n">
         <v>2000009004</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>3001600005</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="0" t="n">
         <v>2000009005</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" s="0" t="n">
         <v>2000009005</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·护甲Lv.5-每只5%(动态)</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="I55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="0" t="n">
         <v>2000010001</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_122</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="C56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
         <is>
           <t>3001700001</t>
         </is>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="0" t="n">
         <v>2000010001</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" s="0" t="n">
         <v>2000010001</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·生命Lv.1-每只1%(动态)</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
+      <c r="I56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="0" t="n">
         <v>2000010002</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_122</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="0" t="n">
         <v>2000010001</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="0" t="inlineStr">
         <is>
           <t>3001700002</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="0" t="n">
         <v>2000010002</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" s="0" t="n">
         <v>2000010002</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·生命Lv.2-每只2%(动态)</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" t="n">
+      <c r="I57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="0" t="n">
         <v>2000010003</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_122</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="0" t="n">
         <v>2000010002</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="0" t="inlineStr">
         <is>
           <t>3001700003</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="0" t="n">
         <v>2000010003</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="0" t="n">
         <v>2000010003</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·生命Lv.3-每只3%(动态)</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="I58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="0" t="n">
         <v>2000010004</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_122</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="0" t="n">
         <v>2000010003</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="0" t="inlineStr">
         <is>
           <t>3001700004</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="0" t="n">
         <v>2000010004</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" s="0" t="n">
         <v>2000010004</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·生命Lv.4-每只4%(动态)</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" t="n">
+      <c r="I59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="0" t="n">
         <v>2000010005</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_122</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="0" t="n">
         <v>2000010004</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="0" t="inlineStr">
         <is>
           <t>3001700005</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="0" t="n">
         <v>2000010005</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" s="0" t="n">
         <v>2000010005</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="0" t="inlineStr">
         <is>
           <t>都是兄弟·生命Lv.5-每只5%(动态)</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="I60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="0" t="n">
         <v>2000011001</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_123</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="inlineStr">
+      <c r="C61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
         <is>
           <t>3001800001</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="0" t="n">
         <v>2000011001</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" s="0" t="n">
         <v>2000011001</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·攻击Lv.1-每只1%(动态)</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="I61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="0" t="n">
         <v>2000011002</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_123</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="0" t="n">
         <v>2000011001</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="0" t="inlineStr">
         <is>
           <t>3001800002</t>
         </is>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="0" t="n">
         <v>2000011002</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" s="0" t="n">
         <v>2000011002</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·攻击Lv.2-每只2%(动态)</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" t="n">
+      <c r="I62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="0" t="n">
         <v>2000011003</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_123</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="0" t="n">
         <v>2000011002</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="0" t="inlineStr">
         <is>
           <t>3001800003</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="0" t="n">
         <v>2000011003</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" s="0" t="n">
         <v>2000011003</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·攻击Lv.3-每只3%(动态)</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" t="n">
+      <c r="I63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="0" t="n">
         <v>2000011004</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_123</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="0" t="n">
         <v>2000011003</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="0" t="inlineStr">
         <is>
           <t>3001800004</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="0" t="n">
         <v>2000011004</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64" s="0" t="n">
         <v>2000011004</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·攻击Lv.4-每只4%(动态)</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="I64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="0" t="n">
         <v>2000011005</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_123</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="0" t="n">
         <v>2000011004</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="0" t="inlineStr">
         <is>
           <t>3001800005</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="0" t="n">
         <v>2000011005</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65" s="0" t="n">
         <v>2000011005</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·攻击Lv.5-每只5%(动态)</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" t="n">
+      <c r="I65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="0" t="n">
         <v>2000012001</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_124</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="C66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
         <is>
           <t>3001900001</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="0" t="n">
         <v>2000012001</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" s="0" t="n">
         <v>2000012001</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·护甲Lv.1-每只1%(动态)</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" t="n">
+      <c r="I66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="0" t="n">
         <v>2000012002</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_124</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="0" t="n">
         <v>2000012001</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="0" t="inlineStr">
         <is>
           <t>3001900002</t>
         </is>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="0" t="n">
         <v>2000012002</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" s="0" t="n">
         <v>2000012002</v>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·护甲Lv.2-每只2%(动态)</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" t="n">
+      <c r="I67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="0" t="n">
         <v>2000012003</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_124</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="0" t="n">
         <v>2000012002</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="0" t="inlineStr">
         <is>
           <t>3001900003</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="0" t="n">
         <v>2000012003</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68" s="0" t="n">
         <v>2000012003</v>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·护甲Lv.3-每只3%(动态)</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" t="n">
+      <c r="I68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="0" t="n">
         <v>2000012004</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_124</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="0" t="n">
         <v>2000012003</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="0" t="inlineStr">
         <is>
           <t>3001900004</t>
         </is>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="0" t="n">
         <v>2000012004</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69" s="0" t="n">
         <v>2000012004</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·护甲Lv.4-每只4%(动态)</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" t="n">
+      <c r="I69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="0" t="n">
         <v>2000012005</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_124</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="0" t="n">
         <v>2000012004</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="0" t="inlineStr">
         <is>
           <t>3001900005</t>
         </is>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="0" t="n">
         <v>2000012005</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" s="0" t="n">
         <v>2000012005</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·护甲Lv.5-每只5%(动态)</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
+      <c r="I70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="0" t="n">
         <v>2000013001</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_125</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="C71" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
         <is>
           <t>3002000001</t>
         </is>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="0" t="n">
         <v>2000013001</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" s="0" t="n">
         <v>2000013001</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·生命Lv.1-每只1%(动态)</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" t="n">
+      <c r="I71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="0" t="n">
         <v>2000013002</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_125</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="0" t="n">
         <v>2000013001</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="0" t="inlineStr">
         <is>
           <t>3002000002</t>
         </is>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="0" t="n">
         <v>2000013002</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="0" t="n">
         <v>2000013002</v>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·生命Lv.2-每只2%(动态)</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" t="n">
+      <c r="I72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="0" t="n">
         <v>2000013003</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_125</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="0" t="n">
         <v>2000013002</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="0" t="inlineStr">
         <is>
           <t>3002000003</t>
         </is>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="0" t="n">
         <v>2000013003</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73" s="0" t="n">
         <v>2000013003</v>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·生命Lv.3-每只3%(动态)</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" t="n">
+      <c r="I73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="0" t="n">
         <v>2000013004</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_125</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="0" t="n">
         <v>2000013003</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="0" t="inlineStr">
         <is>
           <t>3002000004</t>
         </is>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="0" t="n">
         <v>2000013004</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74" s="0" t="n">
         <v>2000013004</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·生命Lv.4-每只4%(动态)</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" t="n">
+      <c r="I74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="0" t="n">
         <v>2000013005</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_125</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="0" t="n">
         <v>2000013004</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="0" t="inlineStr">
         <is>
           <t>3002000005</t>
         </is>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="0" t="n">
         <v>2000013005</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" s="0" t="n">
         <v>2000013005</v>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="0" t="inlineStr">
         <is>
           <t>杀红了眼·生命Lv.5-每只5%(动态)</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="I75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1,177 +1,302 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="AbyssalBlessingInfo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AbyssalBlessingInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>icon_res</t>
+  </si>
+  <si>
+    <t>parent_id</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>buff_ids</t>
+  </si>
+  <si>
+    <t>name[language]</t>
+  </si>
+  <si>
+    <t>details[language_1]</t>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
+  <si>
+    <t>valid</t>
+  </si>
+  <si>
+    <t>max_count</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>图标名字</t>
+  </si>
+  <si>
+    <t>父级深渊馈赠ID</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>名字-中文</t>
+  </si>
+  <si>
+    <t>描述中文</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>是否有效(0无效1有效)</t>
+  </si>
+  <si>
+    <t>一局最多可获得次数(0=不限)</t>
+  </si>
+  <si>
+    <t>ui_abyssalblessing_dna</t>
+  </si>
+  <si>
+    <t>增殖-随机复制一个已有的魔物</t>
+  </si>
+  <si>
+    <t>ui_abyssalblessing_box</t>
+  </si>
+  <si>
+    <t>奖励多多-战斗通关获得的奖励数量+1</t>
+  </si>
+  <si>
+    <t>ui_abyssalblessing_key</t>
+  </si>
+  <si>
+    <t>再来一瓶-战斗通关可选择的奖励次数+1</t>
+  </si>
+  <si>
+    <t>ui_abyssalblessing_money</t>
+  </si>
+  <si>
+    <t>钱多多-每一次击杀有20%的概率多掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>钱多多-每一次击杀有40%的概率多掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>钱多多-每一次击杀有60%的概率多掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>钱多多-每一次击杀有80%的概率多掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>钱多多-每一次击杀有100%的概率多掉落一次魔晶</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -471,162 +596,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -680,74 +802,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1036,483 +1095,389 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J84"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
-    <col width="46.25" customWidth="1" style="1" min="2" max="2"/>
-    <col width="17.5" customWidth="1" style="1" min="3" max="5"/>
-    <col width="17.125" customWidth="1" style="1" min="6" max="6"/>
-    <col width="30.5" customWidth="1" style="1" min="7" max="7"/>
-    <col width="42.875" customWidth="1" style="1" min="8" max="8"/>
-    <col width="25.125" customWidth="1" style="1" min="9" max="9"/>
+    <col min="1" max="1" width="37.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.25" style="1" customWidth="1"/>
+    <col min="3" max="5" width="17.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="42.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>icon_res</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>parent_id</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>buff_ids</t>
-        </is>
-      </c>
-      <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>name[language]</t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>details[language_1]</t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
-        <is>
-          <t>remark</t>
-        </is>
-      </c>
-      <c r="I1" s="0" t="inlineStr">
-        <is>
-          <t>valid</t>
-        </is>
-      </c>
-      <c r="J1" s="0" t="inlineStr">
-        <is>
-          <t>max_count</t>
-        </is>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>图标名字</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>父级深渊馈赠ID</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>buff_ids</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t>名字-中文</t>
-        </is>
-      </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>描述中文</t>
-        </is>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="I3" s="0" t="inlineStr">
-        <is>
-          <t>是否有效(0无效1有效)</t>
-        </is>
-      </c>
-      <c r="J3" s="0" t="inlineStr">
-        <is>
-          <t>一局最多可获得次数(0=不限)</t>
-        </is>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:10">
+      <c r="A4">
         <v>1000001001</v>
       </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_0</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>3000100001</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4">
         <v>1000001001</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4">
         <v>1000001001</v>
       </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t>增殖-随机复制一个已有的魔物</t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="n">
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:10">
+      <c r="A5">
         <v>1000002001</v>
       </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_10</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>3000900001</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5">
         <v>1000002001</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5">
         <v>1000002001</v>
       </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>奖励多多-战斗通关获得的奖励数量+1</t>
-        </is>
-      </c>
-      <c r="I5" s="0" t="n">
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:10">
+      <c r="A6">
         <v>1000003001</v>
       </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_10</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6">
         <v>0</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>3001000001</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6">
         <v>1000003001</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>1000003001</v>
       </c>
-      <c r="H6" s="0" t="inlineStr">
-        <is>
-          <t>再来一瓶-战斗通关可选择的奖励次数+1</t>
-        </is>
-      </c>
-      <c r="I6" s="0" t="n">
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:10">
+      <c r="A7">
         <v>2000001001</v>
       </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>3000200001</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7">
         <v>2000001001</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7">
         <v>2000001001</v>
       </c>
-      <c r="H7" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有20%的概率多掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="n">
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7">
         <v>1</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:10">
+      <c r="A8">
         <v>2000001002</v>
       </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
         <v>2000001001</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>3000200002</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8">
         <v>2000001002</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8">
         <v>2000001002</v>
       </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有40%的概率多掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="n">
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:10">
+      <c r="A9">
         <v>2000001003</v>
       </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9">
         <v>2000001002</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9">
         <v>3</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9">
         <v>3000200003</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9">
         <v>2000001003</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9">
         <v>2000001003</v>
       </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有60%的概率多掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="n">
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9">
         <v>1</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:10">
+      <c r="A10">
         <v>2000001004</v>
       </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10">
         <v>2000001003</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10">
         <v>3000200004</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10">
         <v>2000001004</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10">
         <v>2000001004</v>
       </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有80%的概率多掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="n">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:10">
+      <c r="A11">
         <v>2000001005</v>
       </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>ui_abyssalblessing_9</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11">
         <v>2000001004</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11">
         <v>5</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11">
         <v>3000200005</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11">
         <v>2000001005</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11">
         <v>2000001005</v>
       </c>
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>钱多多-每一次击杀有100%的概率多掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11">
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="1"/>
-    <row r="35" ht="15" customHeight="1" s="1"/>
-    <row r="36" ht="15" customHeight="1" s="1"/>
-    <row r="37" ht="15" customHeight="1" s="1"/>
-    <row r="38" ht="15" customHeight="1" s="1"/>
-    <row r="39" ht="15" customHeight="1" s="1"/>
-    <row r="40" ht="15" customHeight="1" s="1"/>
-    <row r="41" ht="15" customHeight="1" s="1"/>
-    <row r="42" ht="15" customHeight="1" s="1"/>
-    <row r="43" ht="15" customHeight="1" s="1"/>
-    <row r="44" ht="15" customHeight="1" s="1"/>
-    <row r="76" ht="12" customHeight="1" s="1"/>
-    <row r="77" ht="12" customHeight="1" s="1"/>
-    <row r="78" ht="12" customHeight="1" s="1"/>
-    <row r="79" ht="12" customHeight="1" s="1"/>
-    <row r="80" ht="12" customHeight="1" s="1"/>
-    <row r="81" ht="12" customHeight="1" s="1"/>
-    <row r="82" ht="12" customHeight="1" s="1"/>
-    <row r="83" ht="12" customHeight="1" s="1"/>
-    <row r="84" ht="12" customHeight="1" s="1"/>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
+    <row r="37" ht="15" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1"/>
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="15" customHeight="1"/>
+    <row r="44" ht="15" customHeight="1"/>
+    <row r="76" ht="12" customHeight="1"/>
+    <row r="77" ht="12" customHeight="1"/>
+    <row r="78" ht="12" customHeight="1"/>
+    <row r="79" ht="12" customHeight="1"/>
+    <row r="80" ht="12" customHeight="1"/>
+    <row r="81" ht="12" customHeight="1"/>
+    <row r="82" ht="12" customHeight="1"/>
+    <row r="83" ht="12" customHeight="1"/>
+    <row r="84" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1514,7 +1514,7 @@
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv1-每隔3秒落下1道闪电随机击中敌人，对落点0.2范围造成魔王攻击力的伤害</t>
+          <t>闪电Lv1-每隔3秒落下1道闪电随机击中敌人，对落点0.2范围最多1个目标造成魔王攻击力的伤害</t>
         </is>
       </c>
       <c r="I12" s="0" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv2-每隔3秒落下2道闪电随机击中敌人，对落点0.4范围造成魔王攻击力的伤害</t>
+          <t>闪电Lv2-每隔3秒落下2道闪电随机击中敌人，对落点0.4范围最多2个目标造成魔王攻击力的伤害</t>
         </is>
       </c>
       <c r="I13" s="0" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv3-每隔3秒落下3道闪电随机击中敌人，对落点0.6范围造成魔王攻击力的伤害</t>
+          <t>闪电Lv3-每隔3秒落下3道闪电随机击中敌人，对落点0.6范围最多3个目标造成魔王攻击力的伤害</t>
         </is>
       </c>
       <c r="I14" s="0" t="n">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv4-每隔3秒落下4道闪电随机击中敌人，对落点0.8范围造成魔王攻击力的伤害</t>
+          <t>闪电Lv4-每隔3秒落下4道闪电随机击中敌人，对落点0.8范围最多4个目标造成魔王攻击力的伤害</t>
         </is>
       </c>
       <c r="I15" s="0" t="n">
@@ -1633,38 +1633,38 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="0" t="n">
         <v>2000002005</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_thunder</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="0" t="n">
         <v>2000002004</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="0" t="n">
         <v>3000300005</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="0" t="n">
         <v>2000002005</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="0" t="n">
         <v>2000002005</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>闪电Lv5-每隔3秒落下5道闪电随机击中敌人，对落点1范围造成魔王攻击力的伤害</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>闪电Lv5-每隔3秒落下5道闪电随机击中敌人，对落点1范围最多5个目标造成魔王攻击力的伤害</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1665,6 +1665,196 @@
         <v>1</v>
       </c>
       <c r="J16" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2000003001</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_minecar</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3000400001</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2000003001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2000003001</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv1-每5秒随机选1条道路驶出1辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2000003002</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_minecar</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2000003001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3000400002</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2000003002</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2000003002</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv2-每5秒随机选2条道路驶出2辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2000003003</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_minecar</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2000003002</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3000400003</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2000003003</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2000003003</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv3-每5秒随机选3条道路驶出3辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2000003004</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_minecar</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2000003003</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3000400004</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2000003004</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2000003004</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv4-每5秒随机选4条道路驶出4辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2000003005</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_minecar</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2000003004</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3000400005</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2000003005</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2000003005</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv5-每5秒随机选5条道路驶出5辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1669,206 +1669,1335 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="0" t="n">
         <v>2000003001</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_minecar</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>3000400001</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="0" t="n">
         <v>2000003001</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="0" t="n">
         <v>2000003001</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv1-每5秒随机选1条道路驶出1辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="I17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="0" t="n">
         <v>2000003002</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_minecar</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="0" t="n">
         <v>2000003001</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>3000400002</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="0" t="n">
         <v>2000003002</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="0" t="n">
         <v>2000003002</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv2-每5秒随机选2条道路驶出2辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="I18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="0" t="n">
         <v>2000003003</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_minecar</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="0" t="n">
         <v>2000003002</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>3000400003</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="0" t="n">
         <v>2000003003</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="0" t="n">
         <v>2000003003</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv3-每5秒随机选3条道路驶出3辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="I19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="0" t="n">
         <v>2000003004</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_minecar</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="0" t="n">
         <v>2000003003</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>3000400004</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="0" t="n">
         <v>2000003004</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="0" t="n">
         <v>2000003004</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv4-每5秒随机选4条道路驶出4辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="I20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="0" t="n">
         <v>2000003005</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_minecar</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="0" t="n">
         <v>2000003004</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>3000400005</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="0" t="n">
         <v>2000003005</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="0" t="n">
         <v>2000003005</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv5-每5秒随机选5条道路驶出5辆矿车从左向右撞人，第1个目标造成魔王攻击力的伤害，之后每撞1个减半，驶到路尽头消失</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="1"/>
-    <row r="35" ht="15" customHeight="1" s="1"/>
-    <row r="36" ht="15" customHeight="1" s="1"/>
-    <row r="37" ht="15" customHeight="1" s="1"/>
-    <row r="38" ht="15" customHeight="1" s="1"/>
-    <row r="39" ht="15" customHeight="1" s="1"/>
-    <row r="40" ht="15" customHeight="1" s="1"/>
-    <row r="41" ht="15" customHeight="1" s="1"/>
-    <row r="42" ht="15" customHeight="1" s="1"/>
-    <row r="43" ht="15" customHeight="1" s="1"/>
-    <row r="44" ht="15" customHeight="1" s="1"/>
+      <c r="I21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="n">
+        <v>2000004001</v>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boomerang</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>3000500001</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>2000004001</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>2000004001</v>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,随机瞄准敌人,伤害=魔王攻击力,逐目标减半保底1,到达目标后超出一格折返</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="n">
+        <v>2000004002</v>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boomerang</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>2000004001</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>3000500002</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>2000004002</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>2000004002</v>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,随机瞄准敌人,伤害=魔王攻击力,逐目标减半保底1,到达目标后超出一格折返</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="n">
+        <v>2000004003</v>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boomerang</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>2000004002</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>3000500003</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>2000004003</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>2000004003</v>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,随机瞄准敌人,伤害=魔王攻击力,逐目标减半保底1,到达目标后超出一格折返</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="n">
+        <v>2000004004</v>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boomerang</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>2000004003</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>3000500004</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>2000004004</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>2000004004</v>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,随机瞄准敌人,伤害=魔王攻击力,逐目标减半保底1,到达目标后超出一格折返</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="n">
+        <v>2000004005</v>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boomerang</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>2000004004</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>3000500005</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>2000004005</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>2000004005</v>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,随机瞄准敌人,伤害=魔王攻击力,逐目标减半保底1,到达目标后超出一格折返</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_axe</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>3000600001</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,抛物线飞向随机一排最远的敌人,伤害=魔王攻击力</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_axe</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>3000600002</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标1次,伤害逐目标减半保底1</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_axe</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>3000600003</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标2次,伤害逐目标减半保底1</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_axe</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>3000600004</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标3次,伤害逐目标减半保底1</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="n">
+        <v>2000005005</v>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_axe</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>3000600005</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>2000005005</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>2000005005</v>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标4次,伤害逐目标减半保底1</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_book</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>3000700001</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量Lv1-随机一只最前排魔物周围环绕1本书(半径0.75,转速0.6弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_book</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>3000700002</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量Lv2-随机一只最前排魔物周围环绕2本书(半径0.75,转速1.2弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="1">
+      <c r="A34" s="0" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_book</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>3000700003</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量Lv3-随机一只最前排魔物周围环绕3本书(半径0.75,转速1.8弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="1">
+      <c r="A35" s="0" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_book</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>3000700004</t>
+        </is>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量Lv4-随机一只最前排魔物周围环绕4本书(半径0.75,转速2.4弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="1">
+      <c r="A36" s="0" t="n">
+        <v>2000006005</v>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_book</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>3000700005</t>
+        </is>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>2000006005</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>2000006005</v>
+      </c>
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量Lv5-随机一只最前排魔物周围环绕5本书(半径0.75,转速3弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="1">
+      <c r="A37" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_pingpang</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>3000800001</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv1-从魔王处发射1颗菱块(速度2)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="1">
+      <c r="A38" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_pingpang</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>3000800002</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv2-从魔王处发射2颗菱块(速度2.5)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="1">
+      <c r="A39" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_pingpang</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>3000800003</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv3-从魔王处发射3颗菱块(速度3)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="1">
+      <c r="A40" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_pingpang</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>3000800004</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv4-从魔王处发射4颗菱块(速度3.5)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="1">
+      <c r="A41" s="0" t="n">
+        <v>2000007005</v>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_pingpang</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>3000800005</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>2000007005</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>2000007005</v>
+      </c>
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv5-从魔王处发射5颗菱块(速度4)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="1">
+      <c r="A42" s="0" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boom</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>3001100001</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，全道路敌人受魔王攻击力10%伤害并击退0.5</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="1">
+      <c r="A43" s="0" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boom</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>3001100002</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，全道路敌人受魔王攻击力15%伤害并击退0.5</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="1">
+      <c r="A44" s="0" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boom</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>3001100003</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，全道路敌人受魔王攻击力20%伤害并击退0.5</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boom</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>3001100004</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，全道路敌人受魔王攻击力25%伤害并击退0.5</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="n">
+        <v>2000008005</v>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_boom</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>3001100005</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>2000008005</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>2000008005</v>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，全道路敌人受魔王攻击力30%伤害并击退0.5</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_fire</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3001200001</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火Lv1-每10秒投掷1瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_fire</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3001200002</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火Lv2-每10秒投掷2瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_fire</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3001200003</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火Lv3-每10秒投掷3瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_fire</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3001200004</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火Lv4-每10秒投掷4瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2000009005</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ui_abyssalblessing_fire</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3001200005</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2000009005</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2000009005</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火Lv5-每10秒投掷5瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="76" ht="12" customHeight="1" s="1"/>
     <row r="77" ht="12" customHeight="1" s="1"/>
     <row r="78" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -2076,7 +2076,7 @@
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv1-每5秒扔出1把斧头,抛物线飞向随机一排最远的敌人,伤害=魔王攻击力</t>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,抛物线飞向随机一排最远的敌人,伤害=魔王攻击力,命中后弹跳至附近1单位内的另一目标1次,伤害逐目标减半保底1</t>
         </is>
       </c>
       <c r="I27" s="0" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv2-每5秒扔出2把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标1次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标2次,伤害逐目标减半保底1</t>
         </is>
       </c>
       <c r="I28" s="0" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv3-每5秒扔出3把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标2次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标3次,伤害逐目标减半保底1</t>
         </is>
       </c>
       <c r="I29" s="0" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv4-每5秒扔出4把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标3次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标4次,伤害逐目标减半保底1</t>
         </is>
       </c>
       <c r="I30" s="0" t="n">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv5-每5秒扔出5把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标4次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头(首目标互不重复),命中后弹跳至附近1单位内的另一目标5次,伤害逐目标减半保底1</t>
         </is>
       </c>
       <c r="I31" s="0" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv1-随机一只最前排魔物周围环绕1本书(半径0.75,转速0.6弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+          <t>知识的力量Lv1-随机一只最前排魔物周围环绕1本书(半径0.75,转速0.6弧度/秒),触碰敌人造成魔王攻击力40%伤害</t>
         </is>
       </c>
       <c r="I32" s="0" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv2-随机一只最前排魔物周围环绕2本书(半径0.75,转速1.2弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+          <t>知识的力量Lv2-随机一只最前排魔物周围环绕2本书(半径0.75,转速1.2弧度/秒),触碰敌人造成魔王攻击力40%伤害</t>
         </is>
       </c>
       <c r="I33" s="0" t="n">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv3-随机一只最前排魔物周围环绕3本书(半径0.75,转速1.8弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+          <t>知识的力量Lv3-随机一只最前排魔物周围环绕3本书(半径0.75,转速1.8弧度/秒),触碰敌人造成魔王攻击力40%伤害</t>
         </is>
       </c>
       <c r="I34" s="0" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv4-随机一只最前排魔物周围环绕4本书(半径0.75,转速2.4弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+          <t>知识的力量Lv4-随机一只最前排魔物周围环绕4本书(半径0.75,转速2.4弧度/秒),触碰敌人造成魔王攻击力40%伤害</t>
         </is>
       </c>
       <c r="I35" s="0" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv5-随机一只最前排魔物周围环绕5本书(半径0.75,转速3弧度/秒),触碰敌人造成魔王攻击力50%伤害</t>
+          <t>知识的力量Lv5-随机一只最前排魔物周围环绕5本书(半径0.75,转速3弧度/秒),触碰敌人造成魔王攻击力40%伤害</t>
         </is>
       </c>
       <c r="I36" s="0" t="n">
@@ -2809,192 +2809,192 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="0" t="n">
         <v>2000009001</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_fire</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="C47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>3001200001</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="0" t="n">
         <v>2000009001</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="0" t="n">
         <v>2000009001</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>瓶装炼狱火Lv1-每10秒投掷1瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="I47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="0" t="n">
         <v>2000009002</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_fire</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="0" t="n">
         <v>2000009001</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>3001200002</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="0" t="n">
         <v>2000009002</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="0" t="n">
         <v>2000009002</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="0" t="inlineStr">
         <is>
           <t>瓶装炼狱火Lv2-每10秒投掷2瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="I48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="0" t="n">
         <v>2000009003</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_fire</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="0" t="n">
         <v>2000009002</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>3001200003</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="0" t="n">
         <v>2000009003</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="0" t="n">
         <v>2000009003</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>瓶装炼狱火Lv3-每10秒投掷3瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="I49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="0" t="n">
         <v>2000009004</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_fire</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="0" t="n">
         <v>2000009003</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>3001200004</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="0" t="n">
         <v>2000009004</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" s="0" t="n">
         <v>2000009004</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>瓶装炼狱火Lv4-每10秒投掷4瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="I50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="0" t="n">
         <v>2000009005</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>ui_abyssalblessing_fire</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="0" t="n">
         <v>2000009004</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>3001200005</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="0" t="n">
         <v>2000009005</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" s="0" t="n">
         <v>2000009005</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>瓶装炼狱火Lv5-每10秒投掷5瓶炼狱火,落地燃放火焰持续烧灼敌人</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
+      <c r="I51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_abyssal_blessing_info[深渊馈赠信息].xlsx
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-从魔王处发射1颗菱块(速度2)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv1-从魔王处发射1颗菱块(速度2)在道路范围内永久反弹,伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
       <c r="I37" s="0" t="n">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-从魔王处发射2颗菱块(速度2.5)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv2-从魔王处发射2颗菱块(速度2.5)在道路范围内永久反弹,伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
       <c r="I38" s="0" t="n">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-从魔王处发射3颗菱块(速度3)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv3-从魔王处发射3颗菱块(速度3)在道路范围内永久反弹,伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
       <c r="I39" s="0" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-从魔王处发射4颗菱块(速度3.5)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv4-从魔王处发射4颗菱块(速度3.5)在道路范围内永久反弹,伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
       <c r="I40" s="0" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-从魔王处发射5颗菱块(速度4)在道路范围内永久反弹,伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv5-从魔王处发射5颗菱块(速度4)在道路范围内永久反弹,伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
       <c r="I41" s="0" t="n">
